--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484576_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484576_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. EGIDO MUÑOZ</t>
+          <t>L. ALBEROLA GUILLOT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5256</v>
+        <v>2.8178</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5256</v>
+        <v>2.9064</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0.0886</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5256</v>
+        <v>2.3464</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6502</v>
+        <v>1.3618</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8753</v>
+        <v>0.9846</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5256</v>
+        <v>3.5541</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6502</v>
+        <v>2.8577</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8753</v>
+        <v>0.6963</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-1.2077</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.2882</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.7489</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.6452</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.8813</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0.2361</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-2.0063</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-0.6127</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.3937</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. ALBEROLA GUILLOT</t>
+          <t>I. EGIDO MUÑOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4904</v>
+        <v>2.5256</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4799</v>
+        <v>2.5256</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0105</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3464</v>
+        <v>2.5256</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3618</v>
+        <v>0.6502</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9846</v>
+        <v>1.8753</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5541</v>
+        <v>2.5256</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8577</v>
+        <v>0.6502</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6963</v>
+        <v>1.8753</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2077</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2882</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7489</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3178</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4548</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.137</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.0063</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6127</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.415</v>
+        <v>2.1952</v>
       </c>
       <c r="E4" t="n">
-        <v>3.594</v>
+        <v>3.6219</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.179</v>
+        <v>-1.4267</v>
       </c>
       <c r="G4" t="n">
         <v>1.384</v>
@@ -766,13 +766,13 @@
         <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3371</v>
+        <v>1.1173</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5475</v>
+        <v>0.5754</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7896</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>-1.5889</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1882</v>
+        <v>-0.3416</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8345</v>
+        <v>1.2305</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6463</v>
+        <v>-1.572</v>
       </c>
       <c r="G5" t="n">
         <v>0.9515</v>
@@ -844,13 +844,13 @@
         <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8256</v>
+        <v>1.2958</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0136</v>
+        <v>1.4095</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.188</v>
+        <v>-0.1137</v>
       </c>
       <c r="V5" t="n">
         <v>-2.2224</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7716</v>
+        <v>-0.7497</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2316</v>
+        <v>1.3278</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0032</v>
+        <v>-2.0775</v>
       </c>
       <c r="G6" t="n">
         <v>0.5532</v>
@@ -922,13 +922,13 @@
         <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8919</v>
+        <v>-0.8701</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3673</v>
+        <v>-0.2711</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.599</v>
       </c>
       <c r="V6" t="n">
         <v>-1.7156</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6947</v>
+        <v>-0.8616</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7446</v>
+        <v>-1.2087</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0498</v>
+        <v>0.3471</v>
       </c>
       <c r="G7" t="n">
         <v>1.0587</v>
@@ -1000,13 +1000,13 @@
         <v>2.3823</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8659</v>
+        <v>-0.0328</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2217</v>
+        <v>0.3141</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6442</v>
+        <v>-0.3469</v>
       </c>
       <c r="V7" t="n">
         <v>0.3115</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.085</v>
+        <v>-2.2995</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3259</v>
+        <v>-1.367</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7592</v>
+        <v>-0.9326</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6413</v>
@@ -1078,13 +1078,13 @@
         <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5443</v>
+        <v>0.3298</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0196</v>
+        <v>-0.0607</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5639</v>
+        <v>0.3904</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0717</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. CARPITELLI</t>
+          <t>P. LARIO ECHEVARRIAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0326</v>
+        <v>-2.6485</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7992</v>
+        <v>-0.9227</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2334</v>
+        <v>-1.7258</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.2907</v>
+        <v>-2.8482</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.8323</v>
+        <v>-2.8228</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4584</v>
+        <v>-0.0255</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2833</v>
+        <v>-1.0822</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.4341</v>
+        <v>-1.217</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1508</v>
+        <v>0.1349</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0074</v>
+        <v>-1.7661</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3982</v>
+        <v>-1.6057</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6092</v>
+        <v>-0.1603</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3665</v>
+        <v>0.3665</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4661</v>
+        <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5696</v>
+        <v>0.1552</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9947</v>
+        <v>0.1595</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5749</v>
+        <v>-0.0043</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.945</v>
+        <v>-0.3219</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. LARIO ECHEVARRIAS</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0663</v>
+        <v>-2.9699</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2662</v>
+        <v>-1.8277</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8002</v>
+        <v>-1.1422</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8482</v>
+        <v>-5.657</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8228</v>
+        <v>-2.6281</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0255</v>
+        <v>-3.0289</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0822</v>
+        <v>-2.781</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.217</v>
+        <v>-0.3934</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1349</v>
+        <v>-2.3876</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7661</v>
+        <v>-2.876</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6057</v>
+        <v>-2.2347</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1603</v>
+        <v>-0.6413</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3665</v>
+        <v>2.9321</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3665</v>
+        <v>2.9321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2627</v>
+        <v>-1.0633</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.184</v>
+        <v>-0.3137</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.7496</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3219</v>
+        <v>0.8183</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3219</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7338</v>
+        <v>-3.0576</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1363</v>
+        <v>-2.4353</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5975</v>
+        <v>-0.6222</v>
       </c>
       <c r="G11" t="n">
         <v>0.1725</v>
@@ -1312,13 +1312,13 @@
         <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0791</v>
+        <v>-0.4029</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3311</v>
+        <v>0.3699</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7481</v>
+        <v>-0.7728</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9109</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>N. CARPITELLI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0474</v>
+        <v>-4.1918</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.707</v>
+        <v>-2.884</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3404</v>
+        <v>-1.3078</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.657</v>
+        <v>-4.2907</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.6281</v>
+        <v>-3.8323</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0289</v>
+        <v>-0.4584</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.781</v>
+        <v>-2.2833</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3934</v>
+        <v>-2.4341</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.3876</v>
+        <v>0.1508</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.876</v>
+        <v>-2.0074</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.2347</v>
+        <v>-1.3982</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6413</v>
+        <v>-0.6092</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9321</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9321</v>
+        <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.1409</v>
+        <v>1.4104</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.193</v>
+        <v>0.9099</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9478</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8183</v>
+        <v>-0.945</v>
       </c>
       <c r="W12" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4486</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9773</v>
+        <v>-4.6035</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8467</v>
+        <v>-3.4482</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1306</v>
+        <v>-1.1553</v>
       </c>
       <c r="G13" t="n">
         <v>-3.721</v>
@@ -1468,13 +1468,13 @@
         <v>1.6493</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0378</v>
+        <v>0.4116</v>
       </c>
       <c r="T13" t="n">
-        <v>0.218</v>
+        <v>0.6165</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1802</v>
+        <v>-0.205</v>
       </c>
       <c r="V13" t="n">
         <v>-2.0272</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.6779</v>
+        <v>-5.6307</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.2912</v>
+        <v>-4.3184</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3867</v>
+        <v>-1.3124</v>
       </c>
       <c r="G14" t="n">
         <v>-3.5774</v>
@@ -1546,13 +1546,13 @@
         <v>2.7489</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4829</v>
+        <v>-0.4357</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7308</v>
+        <v>0.7036</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2137</v>
+        <v>-1.1393</v>
       </c>
       <c r="V14" t="n">
         <v>-2.5339</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-21.4674</v>
+        <v>-19.8158</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.451499999999999</v>
+        <v>-6.799799999999998</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.0162</v>
+        <v>-13.016</v>
       </c>
       <c r="G15" t="n">
         <v>-11.7437</v>
@@ -1600,10 +1600,10 @@
         <v>2.446499999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0844</v>
+        <v>3.084399999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6379999999999995</v>
+        <v>-0.6380000000000003</v>
       </c>
       <c r="M15" t="n">
         <v>-14.1902</v>
@@ -1612,7 +1612,7 @@
         <v>-13.3869</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8030999999999998</v>
+        <v>-0.8031</v>
       </c>
       <c r="P15" t="n">
         <v>4.5814</v>
@@ -1624,10 +1624,10 @@
         <v>21.0747</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9088000000000013</v>
+        <v>2.5605</v>
       </c>
       <c r="T15" t="n">
-        <v>3.642699999999999</v>
+        <v>5.2942</v>
       </c>
       <c r="U15" t="n">
         <v>-2.734</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>11.8367</v>
+        <v>11.3107</v>
       </c>
       <c r="E16" t="n">
-        <v>8.183199999999999</v>
+        <v>7.3178</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6535</v>
+        <v>3.9929</v>
       </c>
       <c r="G16" t="n">
         <v>7.3911</v>
@@ -1702,13 +1702,13 @@
         <v>2.7489</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5714</v>
+        <v>1.0454</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6282</v>
+        <v>0.7628</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0568</v>
+        <v>0.2826</v>
       </c>
       <c r="V16" t="n">
         <v>3.7905</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.8478</v>
+        <v>6.925</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5179</v>
+        <v>3.3256</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3299</v>
+        <v>3.5993</v>
       </c>
       <c r="G17" t="n">
         <v>1.0648</v>
@@ -1780,13 +1780,13 @@
         <v>2.0158</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5607</v>
+        <v>0.6378</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6214</v>
+        <v>0.4291</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0607</v>
+        <v>0.2087</v>
       </c>
       <c r="V17" t="n">
         <v>4.1229</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.9253</v>
+        <v>6.3487</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5325</v>
+        <v>1.3979</v>
       </c>
       <c r="F18" t="n">
-        <v>4.3928</v>
+        <v>4.9508</v>
       </c>
       <c r="G18" t="n">
         <v>5.3949</v>
@@ -1858,13 +1858,13 @@
         <v>2.7489</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3859</v>
+        <v>0.0375</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9359</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.45</v>
+        <v>0.108</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.6904</v>
+        <v>4.0502</v>
       </c>
       <c r="E19" t="n">
         <v>3.1198</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5706</v>
+        <v>0.9304</v>
       </c>
       <c r="G19" t="n">
         <v>1.7213</v>
@@ -1936,13 +1936,13 @@
         <v>1.4661</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.199</v>
+        <v>0.1608</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0196</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1794</v>
+        <v>0.1804</v>
       </c>
       <c r="V19" t="n">
         <v>0.702</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.7494</v>
+        <v>1.8884</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6358</v>
+        <v>1.7704</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1136</v>
+        <v>0.118</v>
       </c>
       <c r="G20" t="n">
         <v>0.5275</v>
@@ -2014,13 +2014,13 @@
         <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3654</v>
+        <v>0.5043</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3726</v>
+        <v>0.5072</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0072</v>
+        <v>-0.0028</v>
       </c>
       <c r="V20" t="n">
         <v>-0.243</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. DOMINGUEZ ALEIXANDRE</t>
+          <t>J. MARTINEZ TEJERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3784</v>
+        <v>1.6405</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1925</v>
+        <v>0.2196</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8141</v>
+        <v>1.4209</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3279</v>
+        <v>0.6186</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2075</v>
+        <v>0.7277</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5354</v>
+        <v>-0.1091</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1254</v>
+        <v>0.1792</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0837</v>
+        <v>0.0959</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0417</v>
+        <v>0.0833</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4532</v>
+        <v>0.4394</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8762</v>
+        <v>0.6318</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.1925</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0995</v>
+        <v>1.0995</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.733</v>
+        <v>1.0995</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5938</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3658</v>
+        <v>0.0404</v>
       </c>
       <c r="U21" t="n">
-        <v>0.228</v>
+        <v>-0.118</v>
       </c>
       <c r="V21" t="n">
-        <v>2.212</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MARTINEZ TEJERO</t>
+          <t>S. DOMINGUEZ ALEIXANDRE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.982</v>
+        <v>1.2793</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2612</v>
+        <v>2.1925</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2431</v>
+        <v>-0.9132</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6186</v>
+        <v>-0.3279</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7277</v>
+        <v>0.2075</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1091</v>
+        <v>-0.5354</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1792</v>
+        <v>1.1254</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0959</v>
+        <v>1.0837</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0833</v>
+        <v>0.0417</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4394</v>
+        <v>-1.4532</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6318</v>
+        <v>-0.8762</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1925</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0995</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7362</v>
+        <v>0.4947</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4404</v>
+        <v>0.3658</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2958</v>
+        <v>0.129</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.212</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="23">
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>P. BUSTAMANTE CONTRERAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4088</v>
+        <v>-0.0501</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5376</v>
+        <v>0.5661</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1287</v>
+        <v>-0.6162</v>
       </c>
       <c r="G24" t="n">
-        <v>1.3342</v>
+        <v>-0.3664</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3056</v>
+        <v>0.4801</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0286</v>
+        <v>-0.8465</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3551</v>
+        <v>1.0337</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1609</v>
+        <v>1.5914</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.516</v>
+        <v>-0.5577</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6893</v>
+        <v>-1.4002</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1446</v>
+        <v>-1.1113</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5446</v>
+        <v>-0.2888</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.4661</v>
+        <v>-4.2149</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.7489</v>
+        <v>-5.4977</v>
       </c>
       <c r="R24" t="n">
         <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0236</v>
+        <v>0.0283</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5664</v>
+        <v>0.2738</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.59</v>
+        <v>-0.2455</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2534</v>
+        <v>4.503</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4.7563</v>
       </c>
       <c r="X24" t="n">
         <v>-0.2534</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. BUSTAMANTE CONTRERAS</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.5508</v>
+        <v>-0.655</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2031</v>
+        <v>-3.1145</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3477</v>
+        <v>2.4594</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3664</v>
+        <v>1.3342</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4801</v>
+        <v>1.3056</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8465</v>
+        <v>0.0286</v>
       </c>
       <c r="J25" t="n">
-        <v>1.0337</v>
+        <v>-0.3551</v>
       </c>
       <c r="K25" t="n">
-        <v>1.5914</v>
+        <v>0.1609</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5577</v>
+        <v>-0.516</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4002</v>
+        <v>1.6893</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1113</v>
+        <v>1.1446</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2888</v>
+        <v>0.5446</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.2149</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q25" t="n">
-        <v>-5.4977</v>
+        <v>-2.7489</v>
       </c>
       <c r="R25" t="n">
         <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4724</v>
+        <v>-0.2698</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4955</v>
+        <v>-0.0105</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9769</v>
+        <v>-0.2593</v>
       </c>
       <c r="V25" t="n">
-        <v>4.503</v>
+        <v>-0.2534</v>
       </c>
       <c r="W25" t="n">
-        <v>4.7563</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>-0.2534</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D. GONZALEZ FERRER</t>
+          <t>M. CORNEJO GONZALEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.693</v>
+        <v>-1.1899</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2387</v>
+        <v>0.1245</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.4543</v>
+        <v>-1.3144</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.0105</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.443</v>
+        <v>-0.2278</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5675</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.1754</v>
+        <v>1.2054</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.217</v>
+        <v>1.1796</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0417</v>
+        <v>0.0258</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8351</v>
+        <v>-2.0808</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2259</v>
+        <v>-1.4074</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.6092</v>
+        <v>-0.6735</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.1416</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3303</v>
+        <v>0.1365</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3658</v>
+        <v>-0.2781</v>
       </c>
       <c r="V26" t="n">
-        <v>1.0136</v>
+        <v>0.0104</v>
       </c>
       <c r="W26" t="n">
-        <v>1.267</v>
+        <v>-0.3011</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.2534</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>M. CORNEJO GONZALEZ</t>
+          <t>D. GONZALEZ FERRER</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.4531</v>
+        <v>-1.4366</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4525</v>
+        <v>-0.2387</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.0006</v>
+        <v>-1.1979</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-2.0105</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2278</v>
+        <v>-1.443</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.5675</v>
       </c>
       <c r="J27" t="n">
-        <v>1.2054</v>
+        <v>-1.1754</v>
       </c>
       <c r="K27" t="n">
-        <v>1.1796</v>
+        <v>-1.217</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0258</v>
+        <v>0.0417</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.0808</v>
+        <v>-0.8351</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.4074</v>
+        <v>-0.2259</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.6735</v>
+        <v>-0.6092</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.4048</v>
+        <v>-0.4397</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4404</v>
+        <v>-0.3303</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.9643</v>
+        <v>-0.1094</v>
       </c>
       <c r="V27" t="n">
-        <v>0.0104</v>
+        <v>1.0136</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.3011</v>
+        <v>1.267</v>
       </c>
       <c r="X27" t="n">
-        <v>0.3115</v>
+        <v>-0.2534</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.487</v>
+        <v>-5.4477</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.123</v>
+        <v>-4.3153</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3641</v>
+        <v>-1.1324</v>
       </c>
       <c r="G28" t="n">
         <v>-3.3787</v>
@@ -2638,13 +2638,13 @@
         <v>1.2828</v>
       </c>
       <c r="S28" t="n">
-        <v>0.9179</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8416</v>
+        <v>0.6493</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0762</v>
+        <v>0.3079</v>
       </c>
       <c r="V28" t="n">
         <v>-0.6439</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>21.4675</v>
+        <v>25.3137</v>
       </c>
       <c r="E29" t="n">
-        <v>13.0158</v>
+        <v>13.0159</v>
       </c>
       <c r="F29" t="n">
-        <v>8.4514</v>
+        <v>12.2976</v>
       </c>
       <c r="G29" t="n">
         <v>11.7436</v>
@@ -2704,7 +2704,7 @@
         <v>-3.0846</v>
       </c>
       <c r="O29" t="n">
-        <v>0.638</v>
+        <v>0.6380000000000002</v>
       </c>
       <c r="P29" t="n">
         <v>-4.5815</v>
@@ -2716,13 +2716,13 @@
         <v>16.4931</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.9088000000000002</v>
+        <v>2.937200000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>2.733900000000001</v>
+        <v>2.734</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.6427</v>
+        <v>0.2035</v>
       </c>
       <c r="V29" t="n">
         <v>15.2141</v>
